--- a/Luban/Excel/物品.xlsx
+++ b/Luban/Excel/物品.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -104,7 +104,7 @@
           <t xml:space="preserve">
 1 - 药品
 2 - 暗器
-3 - 法器
+3 - 炁具
 4 - 杂物
 5 - 符箓</t>
         </r>
@@ -1735,12 +1735,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
